--- a/routes/rutas_consolidadas.xlsx
+++ b/routes/rutas_consolidadas.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1300,7 +1300,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46121.44693346802</v>
+        <v>46121.44693347222</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>2</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46121.44693346802</v>
+        <v>46121.44693347222</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>3</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46121.44693346802</v>
+        <v>46121.44693347222</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46121.44693346802</v>
+        <v>46121.44693347222</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1424,6 +1424,176 @@
       </c>
       <c r="H29" t="n">
         <v>-76.9969435</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260409_105230</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>46121.453125154</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VICTOR ALVARADO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>JR GAMARRA 564 INT 106  PISO 1  REF LA VICTORIA LA VICTORIA LIMA LIMA PERU</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CHIQUITEX EIRL</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>-12.0633898</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-77.0137431</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260409_105230</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>46121.453125154</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VICTOR ALVARADO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>GAMARRA NRO 564 INT 106 LIMA   PISO 2  REF GAMARRA NRO 564 INT 106 LIMA  LIMA  LA VICTORIA LA VICTORIA LIMA LIMA PERU</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CHIQUITEX EIRL</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>-12.0633604</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-77.0137943</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260409_105230</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>46121.453125154</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VICTOR ALVARADO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>GAMARRA NRO 564 INT 106 LIMA   PISO 2  REF GAMARRA NRO 564 INT 106 LIMA  LIMA  LA VICTORIA LA VICTORIA LIMA LIMA PERU</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CHIQUITEX EIRL</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>-12.0633604</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-77.0137943</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260409_105230</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>46121.453125154</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VICTOR ALVARADO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>GAMARRA NRO 564 INT 106 LIMA   PISO 2  REF GAMARRA NRO 564 INT 106 LIMA  LIMA  LA VICTORIA LA VICTORIA LIMA LIMA PERU</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CHIQUITEX EIRL</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>-12.0633604</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-77.0137943</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260409_105230</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>46121.453125154</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VICTOR ALVARADO</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>JR. PARURO 890 URB. BARRIOS ALTOS</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CHUN KOC SEN S.A.</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>-12.052273</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-77.025171</v>
       </c>
     </row>
   </sheetData>

--- a/routes/rutas_consolidadas.xlsx
+++ b/routes/rutas_consolidadas.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,14 +477,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260409_103227</t>
+          <t>20260409_103330</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46121.43921105324</v>
+        <v>46121.43993920139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -511,14 +511,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260409_103227</t>
+          <t>20260409_103330</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>46121.43921105324</v>
+        <v>46121.43993920139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -527,32 +527,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AV. ALFONSO UGARTE 1426 A 1 CDRA. DE LA PLAZA BOLOGNESI, LIMA, PERU</t>
+          <t>PLAZA BOLOGNESI - PISO 1 - REF PLAZA BOLOGNESI, LIMA, LIMA, LIMA, PERÚ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN FONDO DE INVESTIGADORES Y EDITORES - AFINED</t>
+          <t>ASOCIACIÓN CULTURAL GAMOR</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-12.058712</v>
+        <v>-12.0606794</v>
       </c>
       <c r="H3" t="n">
-        <v>-77.041911</v>
+        <v>-77.041304</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260409_103227</t>
+          <t>20260409_103330</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46121.43921105324</v>
+        <v>46121.43993920139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PLAZA BOLOGNESI - PISO 1 - REF PLAZA BOLOGNESI, LIMA, LIMA, LIMA, PERÚ</t>
+          <t>PLAZA BOLOGNESI 445 - PISO 1 - REF ALT. DE PLAZA BOLOGNESI, LIMA, LIMA, LIMA, PERÚ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -570,23 +570,23 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-12.0606794</v>
+        <v>-12.0607217</v>
       </c>
       <c r="H4" t="n">
-        <v>-77.041304</v>
+        <v>-77.04089329999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260409_103227</t>
+          <t>20260409_103330</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46121.43921105324</v>
+        <v>46121.43993920139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PLAZA BOLOGNESI 445 - PISO 1 - REF ALT. DE PLAZA BOLOGNESI, LIMA, LIMA, LIMA, PERÚ</t>
+          <t>PLAZA BOLOGNESI 445 - PISO 1 - REF PLAZA BOLOGNESI, LIMA, LIMA, LIMA, PERÚ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -613,14 +613,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260409_103227</t>
+          <t>20260409_103956</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46121.43921105324</v>
+        <v>46121.44440482639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -629,32 +629,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PLAZA BOLOGNESI 445 - PISO 1 - REF PLAZA BOLOGNESI, LIMA, LIMA, LIMA, PERÚ</t>
+          <t>CALLE LUIS NATALIO SAENZ 395 A OYAGUE JESUS MARIA LIMA LIMA PERU</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN CULTURAL GAMOR</t>
+          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-12.0607217</v>
+        <v>-12.0683343</v>
       </c>
       <c r="H6" t="n">
-        <v>-77.04089329999999</v>
+        <v>-77.04767629999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260409_103330</t>
+          <t>20260409_103956</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46121.43993920139</v>
+        <v>46121.44440482639</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -663,32 +663,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AV ALFONSO UGARTE 848</t>
+          <t>JR LUIS NATALIO SAENZ 395 FDO OYAGUE  PISO 2  REF ENTRE LA AV ARNALDO MARQUEZ Y AV GARZON JESUS MARIA LIMA LIMA PERU</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ANIMAL DRUG E.I.R.L.</t>
+          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-12.0494369</v>
+        <v>-12.0683343</v>
       </c>
       <c r="H7" t="n">
-        <v>-77.04457309999999</v>
+        <v>-77.04767629999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260409_103330</t>
+          <t>20260409_103956</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46121.43993920139</v>
+        <v>46121.44440482639</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -697,32 +697,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PLAZA BOLOGNESI - PISO 1 - REF PLAZA BOLOGNESI, LIMA, LIMA, LIMA, PERÚ</t>
+          <t>CALLE LUIS NATALIO SAENZ 395 A OYAGUE JESUS MARIA LIMA LIMA PERU</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN CULTURAL GAMOR</t>
+          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-12.0606794</v>
+        <v>-12.0683343</v>
       </c>
       <c r="H8" t="n">
-        <v>-77.041304</v>
+        <v>-77.04767629999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260409_103330</t>
+          <t>20260409_103956</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>46121.43993920139</v>
+        <v>46121.44440482639</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -731,32 +731,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PLAZA BOLOGNESI 445 - PISO 1 - REF ALT. DE PLAZA BOLOGNESI, LIMA, LIMA, LIMA, PERÚ</t>
+          <t>AV. BRASIL 680 URB. BREÑA - PISO 2 - REF JIRON RESTAURACION, BREÑA, LIMA, LIMA, PERÚ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN CULTURAL GAMOR</t>
+          <t>CENTRO ESPECIALIZADO MEDCARE SAC</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-12.0607217</v>
+        <v>-12.0657406</v>
       </c>
       <c r="H9" t="n">
-        <v>-77.04089329999999</v>
+        <v>-77.0463642</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260409_103330</t>
+          <t>20260409_103956</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>46121.43993920139</v>
+        <v>46121.44440482639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -765,835 +765,733 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PLAZA BOLOGNESI 445 - PISO 1 - REF PLAZA BOLOGNESI, LIMA, LIMA, LIMA, PERÚ</t>
+          <t>AV. GARCILASO DE LA VEGA 1261 URB. CER. DE LIMA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN CULTURAL GAMOR</t>
+          <t>CG COMPUGAMER S.A.C.</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-12.0607217</v>
+        <v>-12.0554281</v>
       </c>
       <c r="H10" t="n">
-        <v>-77.04089329999999</v>
+        <v>-77.03804989999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260409_103442</t>
+          <t>20260409_103956</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>46121.44077216435</v>
+        <v>46121.44440482639</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AARÓN GARCÍA</t>
+          <t>ANABEL SANTAMARIA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JR. MANUEL BAÑON 255</t>
+          <t>CA SANTA INES 176 URB COLMENARES PUEBLO LIBRE LIMA LIMA  PISO 2  REF GV ODONTOLOGOS PUEBLO LIBRE LIMA LIMA PERU</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ADECOR S.A.C.</t>
+          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-12.0943283</v>
+        <v>-12.0763991</v>
       </c>
       <c r="H11" t="n">
-        <v>-77.0344983</v>
+        <v>-77.0673068</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260409_103442</t>
+          <t>20260409_103956</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>46121.44077216435</v>
+        <v>46121.44440482639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AARÓN GARCÍA</t>
+          <t>ANABEL SANTAMARIA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AV. SANTO TORIBIO 115</t>
+          <t>JR FELIX DIBOS 1020  PISO SN  REF SR MAGDALENA DEL MAR LIMA LIMA PERU</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGRORIEGO PERU S.A.C.</t>
+          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-12.09606041118146</v>
+        <v>-12.0935526</v>
       </c>
       <c r="H12" t="n">
-        <v>-77.03810978210251</v>
+        <v>-77.06465399999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260409_103442</t>
+          <t>20260409_103956</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>46121.44077216435</v>
+        <v>46121.44440482639</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AARÓN GARCÍA</t>
+          <t>ANABEL SANTAMARIA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AV CAMINO REAL 1049 - PISO UNO - REF SAN ISIDRO, SAN ISIDRO, LIMA, LIMA, PERÚ</t>
+          <t>JR FELIX DIBOS 1020  PISO SN  REF SR MAGDALENA DEL MAR LIMA LIMA PERU</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AGDC PERU</t>
+          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-12.1044195</v>
+        <v>-12.0935526</v>
       </c>
       <c r="H13" t="n">
-        <v>-77.0386819</v>
+        <v>-77.06465399999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260409_103442</t>
+          <t>20260409_103956</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46121.44077216435</v>
+        <v>46121.44440482639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AARÓN GARCÍA</t>
+          <t>ANABEL SANTAMARIA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AV. JAVIER PRADO OESTE 1968 URB. SAN FELIPE</t>
+          <t>AV FELIX DIBOS 1020 URB ORRANTIA DEL MAR  PISO 2  REF AL LADO DE LA SUCAMEC MAGDALENA DEL MAR LIMA LIMA PERU</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ALESAR ULI</t>
+          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-12.094601</v>
+        <v>-12.0965432</v>
       </c>
       <c r="H14" t="n">
-        <v>-77.05191789999999</v>
+        <v>-77.05899920000002</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260409_103442</t>
+          <t>20260409_103956</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46121.44077216435</v>
+        <v>46121.44440482639</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AARÓN GARCÍA</t>
+          <t>ANABEL SANTAMARIA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JR. JOSE ANTONIO 310 URB. PQ. DE MONTERRICO</t>
+          <t>AV FELIX DIBOS 1020 URB ORRANTIA DEL MAR  PISO 2  REF AL LADO DE LA SUCAMEC MAGDALENA DEL MAR LIMA LIMA PERU</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ALESAR ULI</t>
+          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-12.06933499064043</v>
+        <v>-12.0965432</v>
       </c>
       <c r="H15" t="n">
-        <v>-76.96872945209233</v>
+        <v>-77.05899920000002</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260409_103956</t>
+          <t>20260409_104335</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46121.44440482639</v>
+        <v>46121.44693347222</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ANABEL SANTAMARIA</t>
+          <t>LUIS DE LUCIO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CALLE LUIS NATALIO SAENZ 395 A OYAGUE JESUS MARIA LIMA LIMA PERU</t>
+          <t>AV. FLORAL 446 C202 SAN LUIS DE CALIFORNIA COSTADO DE BBVA, TRUJILLO, TRUJILLO,LA LIBERTAD, PERU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
+          <t>CARAMEL CAFÉ</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-12.0683343</v>
+        <v>-8.131491765</v>
       </c>
       <c r="H16" t="n">
-        <v>-77.04767629999999</v>
+        <v>-79.03665664899999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260409_103956</t>
+          <t>20260409_104335</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46121.44440482639</v>
+        <v>46121.44693347222</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ANABEL SANTAMARIA</t>
+          <t>LUIS DE LUCIO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JR LUIS NATALIO SAENZ 395 FDO OYAGUE  PISO 2  REF ENTRE LA AV ARNALDO MARQUEZ Y AV GARZON JESUS MARIA LIMA LIMA PERU</t>
+          <t>CALLE DIAZ DE CIENFUEGOS 287 - PISO 1 - REF AL COSTADO DEL BBVA, TRUJILLO, TRUJILLO, LA LIBERTAD, PERÚ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
+          <t>CARAMEL CAFÉ</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-12.0683343</v>
+        <v>-8.1236347</v>
       </c>
       <c r="H17" t="n">
-        <v>-77.04767629999999</v>
+        <v>-79.0351434</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260409_103956</t>
+          <t>20260409_104335</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>3</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46121.44440482639</v>
+        <v>46121.44693347222</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ANABEL SANTAMARIA</t>
+          <t>LUIS DE LUCIO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CALLE LUIS NATALIO SAENZ 395 A OYAGUE JESUS MARIA LIMA LIMA PERU</t>
+          <t>CALLE CORONEL FRANCISCO BOLOGNESI 502 - PISO 1 - REF CUADRA 5, TRUJILLO, TRUJILLO, LA LIBERTAD, PERÚ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
+          <t>CARAMEL CAFÉ</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-12.0683343</v>
+        <v>-7.8767549</v>
       </c>
       <c r="H18" t="n">
-        <v>-77.04767629999999</v>
+        <v>-79.2940832</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260409_103956</t>
+          <t>20260409_104335</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>4</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46121.44440482639</v>
+        <v>46121.44693347222</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ANABEL SANTAMARIA</t>
+          <t>LUIS DE LUCIO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AV. BRASIL 680 URB. BREÑA - PISO 2 - REF JIRON RESTAURACION, BREÑA, LIMA, LIMA, PERÚ</t>
+          <t>AVENIDA LOS ALAMOS MZ D LOTE 10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CENTRO ESPECIALIZADO MEDCARE SAC</t>
+          <t>LA LEÑA</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-12.0657406</v>
+        <v>-11.9847811</v>
       </c>
       <c r="H19" t="n">
-        <v>-77.0463642</v>
+        <v>-76.9969435</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260409_103956</t>
+          <t>20260409_105230</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46121.44440482639</v>
+        <v>46121.45312515046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ANABEL SANTAMARIA</t>
+          <t>VICTOR ALVARADO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AV. GARCILASO DE LA VEGA 1261 URB. CER. DE LIMA</t>
+          <t>JR GAMARRA 564 INT 106  PISO 1  REF LA VICTORIA LA VICTORIA LIMA LIMA PERU</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CG COMPUGAMER S.A.C.</t>
+          <t>CHIQUITEX EIRL</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-12.0554281</v>
+        <v>-12.0633898</v>
       </c>
       <c r="H20" t="n">
-        <v>-77.03804989999999</v>
+        <v>-77.0137431</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260409_103956</t>
+          <t>20260409_105230</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46121.44440482639</v>
+        <v>46121.45312515046</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ANABEL SANTAMARIA</t>
+          <t>VICTOR ALVARADO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CA SANTA INES 176 URB COLMENARES PUEBLO LIBRE LIMA LIMA  PISO 2  REF GV ODONTOLOGOS PUEBLO LIBRE LIMA LIMA PERU</t>
+          <t>GAMARRA NRO 564 INT 106 LIMA   PISO 2  REF GAMARRA NRO 564 INT 106 LIMA  LIMA  LA VICTORIA LA VICTORIA LIMA LIMA PERU</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
+          <t>CHIQUITEX EIRL</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-12.0763991</v>
+        <v>-12.0633604</v>
       </c>
       <c r="H21" t="n">
-        <v>-77.0673068</v>
+        <v>-77.0137943</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260409_103956</t>
+          <t>20260409_105230</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46121.44440482639</v>
+        <v>46121.45312515046</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ANABEL SANTAMARIA</t>
+          <t>VICTOR ALVARADO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>JR FELIX DIBOS 1020  PISO SN  REF SR MAGDALENA DEL MAR LIMA LIMA PERU</t>
+          <t>GAMARRA NRO 564 INT 106 LIMA   PISO 2  REF GAMARRA NRO 564 INT 106 LIMA  LIMA  LA VICTORIA LA VICTORIA LIMA LIMA PERU</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
+          <t>CHIQUITEX EIRL</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-12.0935526</v>
+        <v>-12.0633604</v>
       </c>
       <c r="H22" t="n">
-        <v>-77.06465399999999</v>
+        <v>-77.0137943</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260409_103956</t>
+          <t>20260409_105230</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46121.44440482639</v>
+        <v>46121.45312515046</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ANABEL SANTAMARIA</t>
+          <t>VICTOR ALVARADO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>JR FELIX DIBOS 1020  PISO SN  REF SR MAGDALENA DEL MAR LIMA LIMA PERU</t>
+          <t>GAMARRA NRO 564 INT 106 LIMA   PISO 2  REF GAMARRA NRO 564 INT 106 LIMA  LIMA  LA VICTORIA LA VICTORIA LIMA LIMA PERU</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
+          <t>CHIQUITEX EIRL</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-12.0935526</v>
+        <v>-12.0633604</v>
       </c>
       <c r="H23" t="n">
-        <v>-77.06465399999999</v>
+        <v>-77.0137943</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260409_103956</t>
+          <t>20260409_105230</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46121.44440482639</v>
+        <v>46121.45312515046</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ANABEL SANTAMARIA</t>
+          <t>VICTOR ALVARADO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AV FELIX DIBOS 1020 URB ORRANTIA DEL MAR  PISO 2  REF AL LADO DE LA SUCAMEC MAGDALENA DEL MAR LIMA LIMA PERU</t>
+          <t>JR. PARURO 890 URB. BARRIOS ALTOS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
+          <t>CHUN KOC SEN S.A.</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-12.0965432</v>
+        <v>-12.052273</v>
       </c>
       <c r="H24" t="n">
-        <v>-77.05899920000002</v>
+        <v>-77.025171</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260409_103956</t>
+          <t>20260409_110521</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46121.44440482639</v>
+        <v>46121.4620496412</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ANABEL SANTAMARIA</t>
+          <t>MONICA VALENZUELA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AV FELIX DIBOS 1020 URB ORRANTIA DEL MAR  PISO 2  REF AL LADO DE LA SUCAMEC MAGDALENA DEL MAR LIMA LIMA PERU</t>
+          <t>AVENIDA ESPAÑA 2144 TRUJILLO - PISO 1 - REF FRENTE AL CC PROTECTOR, TRUJILLO, TRUJILLO, LA LIBERTAD, PERÚ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CENTRO ODONTOLÓGICO GIL VÁSQUEZ</t>
+          <t>BENDEZU MORA JOSE ANTONIO</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-12.0965432</v>
+        <v>-8.113788099999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-77.05899920000002</v>
+        <v>-79.024085</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260409_104335</t>
+          <t>20260409_110521</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46121.44693347222</v>
+        <v>46121.4620496412</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LUIS DE LUCIO</t>
+          <t>MONICA VALENZUELA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AV. FLORAL 446 C202 SAN LUIS DE CALIFORNIA COSTADO DE BBVA, TRUJILLO, TRUJILLO,LA LIBERTAD, PERU</t>
+          <t>AV GUARDIA CIVIL 380 - PISO - - REF FRENTE AL MERCADO SANTA ROSA, CHORRILLOS, LIMA, LIMA, PERÚ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CARAMEL CAFÉ</t>
+          <t>AVENTURA GYM CHORRILLOS</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-8.131491765</v>
+        <v>-12.1838275</v>
       </c>
       <c r="H26" t="n">
-        <v>-79.03665664899999</v>
+        <v>-77.0009704</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260409_104335</t>
+          <t>20260409_110521</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46121.44693347222</v>
+        <v>46121.4620496412</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LUIS DE LUCIO</t>
+          <t>MONICA VALENZUELA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CALLE DIAZ DE CIENFUEGOS 287 - PISO 1 - REF AL COSTADO DEL BBVA, TRUJILLO, TRUJILLO, LA LIBERTAD, PERÚ</t>
+          <t>MZA A LOTE 9 ASC NAVIDAD DE VILLA LIMA, CHORRILLOS, LIMA, LIMA, PERU</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CARAMEL CAFÉ</t>
+          <t>AUTOPARTES IMPORTACION S.A.C.</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-8.1236347</v>
+        <v>-12.1899097</v>
       </c>
       <c r="H27" t="n">
-        <v>-79.0351434</v>
+        <v>-77.0039062</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260409_104335</t>
+          <t>20260409_110521</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46121.44693347222</v>
+        <v>46121.4620496412</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LUIS DE LUCIO</t>
+          <t>MONICA VALENZUELA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CALLE CORONEL FRANCISCO BOLOGNESI 502 - PISO 1 - REF CUADRA 5, TRUJILLO, TRUJILLO, LA LIBERTAD, PERÚ</t>
+          <t>MZA A LOTE 9 ASC NAVIDAD DE VILLA LIMA, CHORRILLOS, LIMA, LIMA, PERU</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CARAMEL CAFÉ</t>
+          <t>AUTOPARTES IMPORTACION S.A.C.</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-7.8767549</v>
+        <v>-12.1899097</v>
       </c>
       <c r="H28" t="n">
-        <v>-79.2940832</v>
+        <v>-77.0039062</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260409_104335</t>
+          <t>20260409_110521</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46121.44693347222</v>
+        <v>46121.4620496412</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LUIS DE LUCIO</t>
+          <t>MONICA VALENZUELA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AVENIDA LOS ALAMOS MZ D LOTE 10</t>
+          <t>MZ A LT 9 NAVIDAD DE VILLA, CHORRILLOS, LIMA, LIMA, PERÚ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>LA LEÑA</t>
+          <t>AUTOPARTES IMPORTACION S.A.C.</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-11.9847811</v>
+        <v>-12.1909281</v>
       </c>
       <c r="H29" t="n">
-        <v>-76.9969435</v>
+        <v>-77.005076</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260409_105230</t>
+          <t>20260409_110521</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46121.453125154</v>
+        <v>46121.4620496412</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VICTOR ALVARADO</t>
+          <t>MONICA VALENZUELA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>JR GAMARRA 564 INT 106  PISO 1  REF LA VICTORIA LA VICTORIA LIMA LIMA PERU</t>
+          <t>MZ A LT 9 NAVIDAD DE VILLA, CHORRILLOS, LIMA, LIMA, PERÚ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CHIQUITEX EIRL</t>
+          <t>AUTOPARTES IMPORTACION S.A.C.</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-12.0633898</v>
+        <v>-12.1909281</v>
       </c>
       <c r="H30" t="n">
-        <v>-77.0137431</v>
+        <v>-77.005076</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260409_105230</t>
+          <t>20260409_110521</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46121.453125154</v>
+        <v>46121.4620496412</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VICTOR ALVARADO</t>
+          <t>MONICA VALENZUELA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GAMARRA NRO 564 INT 106 LIMA   PISO 2  REF GAMARRA NRO 564 INT 106 LIMA  LIMA  LA VICTORIA LA VICTORIA LIMA LIMA PERU</t>
+          <t>MZ A LT 9 NAVIDAD DE VILLA, CHORRILLOS, LIMA, LIMA, PERÚ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CHIQUITEX EIRL</t>
+          <t>AUTOPARTES IMPORTACION S.A.C.</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-12.0633604</v>
+        <v>-12.1909281</v>
       </c>
       <c r="H31" t="n">
-        <v>-77.0137943</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>20260409_105230</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>46121.453125154</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>VICTOR ALVARADO</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>GAMARRA NRO 564 INT 106 LIMA   PISO 2  REF GAMARRA NRO 564 INT 106 LIMA  LIMA  LA VICTORIA LA VICTORIA LIMA LIMA PERU</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>CHIQUITEX EIRL</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>-12.0633604</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.0137943</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>20260409_105230</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>46121.453125154</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>VICTOR ALVARADO</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>GAMARRA NRO 564 INT 106 LIMA   PISO 2  REF GAMARRA NRO 564 INT 106 LIMA  LIMA  LA VICTORIA LA VICTORIA LIMA LIMA PERU</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>CHIQUITEX EIRL</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>-12.0633604</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-77.0137943</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>20260409_105230</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>46121.453125154</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>VICTOR ALVARADO</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>JR. PARURO 890 URB. BARRIOS ALTOS</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>CHUN KOC SEN S.A.</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>-12.052273</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-77.025171</v>
+        <v>-77.005076</v>
       </c>
     </row>
   </sheetData>
